--- a/Excel Projects/Excel Project Dataset.xlsx
+++ b/Excel Projects/Excel Project Dataset.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GIT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GIT\Excel Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F7C75A7-9788-4021-93A3-1A8A1180918E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9630" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Pivot Table" sheetId="6" r:id="rId1"/>
@@ -198,7 +197,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -761,67 +760,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="32">
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
@@ -985,47 +924,6 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="1"/>
@@ -1041,47 +939,6 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -1135,10 +992,10 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>53449.612403100778</c:v>
+                  <c:v>66000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>56520.146520146518</c:v>
+                  <c:v>70000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1194,10 +1051,10 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>55267.489711934155</c:v>
+                  <c:v>61296.296296296299</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>59603.174603174601</c:v>
+                  <c:v>68048.780487804877</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1534,6 +1391,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1541,7 +1399,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1626,47 +1483,6 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="1"/>
@@ -1682,47 +1498,6 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -1786,19 +1561,19 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>171</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>80</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>93</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>67</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>120</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1866,19 +1641,19 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>207</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>33</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>83</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>95</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>77</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2122,6 +1897,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2129,7 +1905,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2294,47 +2069,6 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="1"/>
@@ -2350,47 +2084,6 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -2446,14 +2139,11 @@
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>71</c:v>
-                </c:pt>
                 <c:pt idx="1">
-                  <c:v>326</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>134</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2512,13 +2202,13 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>41</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>393</c:v>
+                  <c:v>84</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>61</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2761,6 +2451,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2768,7 +2459,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2853,47 +2543,6 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="1"/>
@@ -2909,47 +2558,6 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -2982,329 +2590,215 @@
           </c:spPr>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot Table'!$A$68:$A$121</c:f>
+              <c:f>'Pivot Table'!$A$68:$A$105</c:f>
               <c:strCache>
-                <c:ptCount val="53"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>27</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>28</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>29</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>32</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>33</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>34</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>35</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>36</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>37</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>39</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>40</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>41</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>42</c:v>
+                  <c:v>47</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>43</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>44</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>45</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>47</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>48</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>49</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>50</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>51</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>52</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>53</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>54</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>55</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>56</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>57</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>58</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>59</c:v>
+                  <c:v>73</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>60</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>61</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>62</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>63</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>66</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>67</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>68</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>71</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>72</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>73</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>74</c:v>
-                </c:pt>
-                <c:pt idx="50">
                   <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>89</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot Table'!$B$68:$B$121</c:f>
+              <c:f>'Pivot Table'!$B$68:$B$105</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="53"/>
-                <c:pt idx="0">
+                <c:ptCount val="37"/>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>15</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>12</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>23</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>18</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>15</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>17</c:v>
-                </c:pt>
                 <c:pt idx="19">
-                  <c:v>16</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>18</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>12</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>16</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>15</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>13</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>10</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>10</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>11</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>5</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>14</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>14</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>8</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="48">
                   <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3340,319 +2834,211 @@
           </c:spPr>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot Table'!$A$68:$A$121</c:f>
+              <c:f>'Pivot Table'!$A$68:$A$105</c:f>
               <c:strCache>
-                <c:ptCount val="53"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>27</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>28</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>29</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>32</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>33</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>34</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>35</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>36</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>37</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>39</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>40</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>41</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>42</c:v>
+                  <c:v>47</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>43</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>44</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>45</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>47</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>48</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>49</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>50</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>51</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>52</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>53</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>54</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>55</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>56</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>57</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>58</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>59</c:v>
+                  <c:v>73</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>60</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>61</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>62</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>63</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>66</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>67</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>68</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>71</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>72</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>73</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>74</c:v>
-                </c:pt>
-                <c:pt idx="50">
                   <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>89</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot Table'!$C$68:$C$121</c:f>
+              <c:f>'Pivot Table'!$C$68:$C$105</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>9</c:v>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>8</c:v>
+                <c:pt idx="5">
+                  <c:v>12</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>10</c:v>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>20</c:v>
-                </c:pt>
                 <c:pt idx="23">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>8</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>15</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>6</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>4</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>4</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>7</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>7</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="50">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -3823,6 +3209,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3830,7 +3217,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4219,47 +3605,6 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="5"/>
@@ -4275,47 +3620,6 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -4369,10 +3673,10 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>53449.612403100778</c:v>
+                  <c:v>66000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>56520.146520146518</c:v>
+                  <c:v>70000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4428,10 +3732,10 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>55267.489711934155</c:v>
+                  <c:v>61296.296296296299</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>59603.174603174601</c:v>
+                  <c:v>68048.780487804877</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4624,6 +3928,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -4737,6 +4042,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4768,6 +4074,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4775,7 +4082,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4996,47 +4302,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="5"/>
@@ -5065,47 +4330,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -5182,19 +4406,19 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>171</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>80</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>93</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>67</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>120</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5275,19 +4499,19 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>207</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>33</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>83</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>95</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>77</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5360,6 +4584,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -5497,6 +4722,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5528,6 +4754,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5535,7 +4762,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5928,6 +5154,7 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -5965,7 +5192,9 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -5985,6 +5214,7 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -6022,7 +5252,9 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -6097,6 +5329,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -6138,14 +5371,11 @@
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>71</c:v>
-                </c:pt>
                 <c:pt idx="1">
-                  <c:v>326</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>134</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6220,6 +5450,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -6262,13 +5493,13 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>41</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>393</c:v>
+                  <c:v>84</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>61</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6342,6 +5573,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -6481,6 +5713,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6512,6 +5745,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6519,7 +5753,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6828,47 +6061,6 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="5"/>
@@ -6884,47 +6076,6 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -6957,329 +6108,215 @@
           </c:spPr>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot Table'!$A$68:$A$121</c:f>
+              <c:f>'Pivot Table'!$A$68:$A$105</c:f>
               <c:strCache>
-                <c:ptCount val="53"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>27</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>28</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>29</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>32</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>33</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>34</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>35</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>36</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>37</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>39</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>40</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>41</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>42</c:v>
+                  <c:v>47</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>43</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>44</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>45</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>47</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>48</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>49</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>50</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>51</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>52</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>53</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>54</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>55</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>56</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>57</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>58</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>59</c:v>
+                  <c:v>73</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>60</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>61</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>62</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>63</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>66</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>67</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>68</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>71</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>72</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>73</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>74</c:v>
-                </c:pt>
-                <c:pt idx="50">
                   <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>89</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot Table'!$B$68:$B$121</c:f>
+              <c:f>'Pivot Table'!$B$68:$B$105</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="53"/>
-                <c:pt idx="0">
+                <c:ptCount val="37"/>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>15</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>12</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>23</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>18</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>15</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>17</c:v>
-                </c:pt>
                 <c:pt idx="19">
-                  <c:v>16</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>18</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>12</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>16</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>15</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>13</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>10</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>10</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>11</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>5</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>14</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>14</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>8</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="48">
                   <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7315,319 +6352,211 @@
           </c:spPr>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot Table'!$A$68:$A$121</c:f>
+              <c:f>'Pivot Table'!$A$68:$A$105</c:f>
               <c:strCache>
-                <c:ptCount val="53"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>27</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>28</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>29</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>32</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>33</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>34</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>35</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>36</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>37</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>39</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>40</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>41</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>42</c:v>
+                  <c:v>47</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>43</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>44</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>45</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>47</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>48</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>49</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>50</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>51</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>52</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>53</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>54</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>55</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>56</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>57</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>58</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>59</c:v>
+                  <c:v>73</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>60</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>61</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>62</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>63</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>66</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>67</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>68</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>71</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>72</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>73</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>74</c:v>
-                </c:pt>
-                <c:pt idx="50">
                   <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>89</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot Table'!$C$68:$C$121</c:f>
+              <c:f>'Pivot Table'!$C$68:$C$105</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>9</c:v>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>8</c:v>
+                <c:pt idx="5">
+                  <c:v>12</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>10</c:v>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>20</c:v>
-                </c:pt>
                 <c:pt idx="23">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>8</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>15</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>6</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>4</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>4</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>7</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>7</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="50">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -7767,6 +6696,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7798,6 +6728,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7805,7 +6736,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -12829,7 +11759,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Moorche" refreshedDate="46006.52022997685" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="1026" xr:uid="{AEA7DCB0-CEAB-4F04-9AE4-5D6A2A0AF212}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Moorche" refreshedDate="46006.52022997685" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="1026">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:N1027" sheet="bike_buyers"/>
   </cacheSource>
@@ -29407,8 +28337,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E9F5B5AC-C801-4F07-B87C-43B3C63FEF66}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="A66:D121" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A45:D50" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -29449,11 +28379,585 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
+        <item h="1" x="0"/>
+        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
         <item x="0"/>
         <item x="4"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
         <item x="2"/>
         <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="13"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="12"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Purchased Bike" fld="12" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="8">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="6">
+    <chartFormat chart="2" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="A3:D7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="164" showAll="0">
+      <items count="17">
+        <item x="4"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="14"/>
+        <item x="10"/>
         <item x="3"/>
+        <item x="2"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="15"/>
+        <item x="7"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="5"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="0"/>
+        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="12"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Income" fld="3" subtotal="average" baseField="2" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="9">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A23:D30" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="17">
+        <item x="4"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="14"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="15"/>
+        <item x="7"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="5"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="0"/>
+        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="12"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Purchased Bike" fld="12" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="10">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="A66:D105" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="17">
+        <item x="4"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="14"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="15"/>
+        <item x="7"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="5"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="0"/>
+        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -29555,27 +29059,12 @@
   <rowFields count="1">
     <field x="11"/>
   </rowFields>
-  <rowItems count="54">
+  <rowItems count="38">
     <i>
       <x/>
     </i>
     <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
       <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
     </i>
     <i>
       <x v="7"/>
@@ -29629,13 +29118,7 @@
       <x v="23"/>
     </i>
     <i>
-      <x v="24"/>
-    </i>
-    <i>
       <x v="25"/>
-    </i>
-    <i>
-      <x v="26"/>
     </i>
     <i>
       <x v="27"/>
@@ -29644,31 +29127,10 @@
       <x v="28"/>
     </i>
     <i>
-      <x v="29"/>
-    </i>
-    <i>
       <x v="30"/>
     </i>
     <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="32"/>
-    </i>
-    <i>
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="34"/>
-    </i>
-    <i>
-      <x v="35"/>
-    </i>
-    <i>
       <x v="36"/>
-    </i>
-    <i>
-      <x v="37"/>
     </i>
     <i>
       <x v="38"/>
@@ -29709,12 +29171,6 @@
     <i>
       <x v="50"/>
     </i>
-    <i>
-      <x v="51"/>
-    </i>
-    <i>
-      <x v="52"/>
-    </i>
     <i t="grand">
       <x/>
     </i>
@@ -29737,7 +29193,7 @@
     <dataField name="Count of Purchased Bike" fld="12" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="28">
+    <format dxfId="11">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -29827,582 +29283,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{27692988-97B5-473A-AC25-0166831399F8}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A45:D50" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0">
-      <items count="17">
-        <item x="4"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="14"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="8"/>
-        <item x="11"/>
-        <item x="15"/>
-        <item x="7"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="5"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="13"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="12"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Purchased Bike" fld="12" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="29">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="6">
-    <chartFormat chart="2" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9932A7E-9555-4332-9170-810E7E4B60AB}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
-  <location ref="A3:D7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="164" showAll="0">
-      <items count="17">
-        <item x="4"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="14"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="8"/>
-        <item x="11"/>
-        <item x="15"/>
-        <item x="7"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="5"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="12"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Income" fld="3" subtotal="average" baseField="2" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="30">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{65ADDB42-B028-4B4D-8AAF-77BCA17A7DD4}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="A23:D30" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0">
-      <items count="17">
-        <item x="4"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="14"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="8"/>
-        <item x="11"/>
-        <item x="15"/>
-        <item x="7"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="5"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="12"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Purchased Bike" fld="12" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="31">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="1" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Marital_Status" xr10:uid="{8D3B58EB-C6B9-4DB0-8BB1-0B8D0C4FBE96}" sourceName="Marital Status">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_Marital_Status" sourceName="Marital Status">
   <pivotTables>
     <pivotTable tabId="6" name="PivotTable8"/>
     <pivotTable tabId="6" name="PivotTable1"/>
@@ -30421,7 +29303,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Region" xr10:uid="{97451935-7564-4E06-A977-455D43BDB90C}" sourceName="Region">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_Region" sourceName="Region">
   <pivotTables>
     <pivotTable tabId="6" name="PivotTable7"/>
     <pivotTable tabId="6" name="PivotTable1"/>
@@ -30441,7 +29323,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Education" xr10:uid="{377F424C-EAF3-4471-B083-85F264A733C9}" sourceName="Education">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_Education" sourceName="Education">
   <pivotTables>
     <pivotTable tabId="6" name="PivotTable7"/>
     <pivotTable tabId="6" name="PivotTable1"/>
@@ -30451,11 +29333,11 @@
   <data>
     <tabular pivotCacheId="2014493951">
       <items count="5">
-        <i x="0" s="1"/>
+        <i x="0"/>
         <i x="4" s="1"/>
-        <i x="2" s="1"/>
-        <i x="1" s="1"/>
-        <i x="3" s="1"/>
+        <i x="2"/>
+        <i x="1"/>
+        <i x="3"/>
       </items>
     </tabular>
   </data>
@@ -30463,10 +29345,10 @@
 </file>
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Marital Status" xr10:uid="{F28DB391-D338-48B7-B5DD-04806161923C}" cache="Slicer_Marital_Status" caption="Marital Status" rowHeight="241300"/>
-  <slicer name="Region 1" xr10:uid="{D9C5262C-457B-4B84-AC88-08EEF6EB0512}" cache="Slicer_Region" caption="Region" rowHeight="241300"/>
-  <slicer name="Education" xr10:uid="{51635F34-9AD1-4101-B0D5-914AF67FA38E}" cache="Slicer_Education" caption="Education" rowHeight="241300"/>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <slicer name="Marital Status" cache="Slicer_Marital_Status" caption="Marital Status" rowHeight="241300"/>
+  <slicer name="Region 1" cache="Slicer_Region" caption="Region" rowHeight="241300"/>
+  <slicer name="Education" cache="Slicer_Education" caption="Education" rowHeight="241300"/>
 </slicers>
 </file>
 
@@ -30766,13 +29648,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63B1BC3F-AEBC-4015-B13B-370384DDA54E}">
-  <dimension ref="A3:D121"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:D105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.85546875" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" customWidth="1"/>
     <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="10" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="17" width="11.140625" bestFit="1" customWidth="1"/>
@@ -30810,13 +29692,13 @@
         <v>33</v>
       </c>
       <c r="B5" s="5">
-        <v>53449.612403100778</v>
+        <v>66000</v>
       </c>
       <c r="C5" s="5">
-        <v>55267.489711934155</v>
+        <v>61296.296296296299</v>
       </c>
       <c r="D5" s="5">
-        <v>54331.337325349305</v>
+        <v>63297.872340425529</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -30824,13 +29706,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>56520.146520146518</v>
+        <v>70000</v>
       </c>
       <c r="C6" s="5">
-        <v>59603.174603174601</v>
+        <v>68048.780487804877</v>
       </c>
       <c r="D6" s="5">
-        <v>58000</v>
+        <v>69012.345679012345</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -30838,13 +29720,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="5">
-        <v>55028.248587570619</v>
+        <v>68000</v>
       </c>
       <c r="C7" s="5">
-        <v>57474.747474747477</v>
+        <v>64210.526315789473</v>
       </c>
       <c r="D7" s="5">
-        <v>56208.576998050681</v>
+        <v>65942.857142857145</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -30874,13 +29756,13 @@
         <v>16</v>
       </c>
       <c r="B25" s="5">
-        <v>171</v>
+        <v>42</v>
       </c>
       <c r="C25" s="5">
-        <v>207</v>
+        <v>51</v>
       </c>
       <c r="D25" s="5">
-        <v>378</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -30888,13 +29770,13 @@
         <v>30</v>
       </c>
       <c r="B26" s="5">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C26" s="5">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D26" s="5">
-        <v>113</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -30902,13 +29784,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="5">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="C27" s="5">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="D27" s="5">
-        <v>176</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -30916,13 +29798,13 @@
         <v>22</v>
       </c>
       <c r="B28" s="5">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="C28" s="5">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="D28" s="5">
-        <v>162</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -30930,13 +29812,13 @@
         <v>23</v>
       </c>
       <c r="B29" s="5">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="C29" s="5">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="D29" s="5">
-        <v>197</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -30944,13 +29826,13 @@
         <v>37</v>
       </c>
       <c r="B30" s="5">
-        <v>531</v>
+        <v>80</v>
       </c>
       <c r="C30" s="5">
-        <v>495</v>
+        <v>95</v>
       </c>
       <c r="D30" s="5">
-        <v>1026</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -30979,14 +29861,12 @@
       <c r="A47" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="5">
-        <v>71</v>
-      </c>
+      <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D47" s="5">
-        <v>112</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -30994,13 +29874,13 @@
         <v>43</v>
       </c>
       <c r="B48" s="5">
-        <v>326</v>
+        <v>58</v>
       </c>
       <c r="C48" s="5">
-        <v>393</v>
+        <v>84</v>
       </c>
       <c r="D48" s="5">
-        <v>719</v>
+        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -31008,13 +29888,13 @@
         <v>44</v>
       </c>
       <c r="B49" s="5">
-        <v>134</v>
+        <v>22</v>
       </c>
       <c r="C49" s="5">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="D49" s="5">
-        <v>195</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -31022,13 +29902,13 @@
         <v>37</v>
       </c>
       <c r="B50" s="5">
-        <v>531</v>
+        <v>80</v>
       </c>
       <c r="C50" s="5">
-        <v>495</v>
+        <v>95</v>
       </c>
       <c r="D50" s="5">
-        <v>1026</v>
+        <v>175</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -31057,742 +29937,498 @@
       <c r="A68" s="4">
         <v>25</v>
       </c>
-      <c r="B68" s="5">
-        <v>2</v>
-      </c>
+      <c r="B68" s="5"/>
       <c r="C68" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D68" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
-        <v>26</v>
-      </c>
-      <c r="B69" s="5">
-        <v>8</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B69" s="5"/>
       <c r="C69" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D69" s="5">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B70" s="5">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C70" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D70" s="5">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B71" s="5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C71" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D71" s="5">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B72" s="5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C72" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D72" s="5">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B73" s="5">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C73" s="5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D73" s="5">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B74" s="5">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C74" s="5">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D74" s="5">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B75" s="5">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C75" s="5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D75" s="5">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
-        <v>33</v>
-      </c>
-      <c r="B76" s="5">
-        <v>8</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B76" s="5"/>
       <c r="C76" s="5">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D76" s="5">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B77" s="5">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C77" s="5">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D77" s="5">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B78" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C78" s="5">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D78" s="5">
-        <v>40</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B79" s="5">
-        <v>8</v>
-      </c>
-      <c r="C79" s="5">
-        <v>31</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C79" s="5"/>
       <c r="D79" s="5">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
-        <v>37</v>
-      </c>
-      <c r="B80" s="5">
-        <v>4</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B80" s="5"/>
       <c r="C80" s="5">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D80" s="5">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B81" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C81" s="5">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D81" s="5">
-        <v>38</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B82" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C82" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D82" s="5">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B83" s="5">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C83" s="5">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D83" s="5">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B84" s="5">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C84" s="5">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D84" s="5">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B85" s="5">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C85" s="5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D85" s="5">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B86" s="5">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C86" s="5">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D86" s="5">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B87" s="5">
-        <v>16</v>
-      </c>
-      <c r="C87" s="5">
-        <v>12</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C87" s="5"/>
       <c r="D87" s="5">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B88" s="5">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C88" s="5">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D88" s="5">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B89" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C89" s="5">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D89" s="5">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B90" s="5">
-        <v>20</v>
-      </c>
-      <c r="C90" s="5">
-        <v>20</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C90" s="5"/>
       <c r="D90" s="5">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
-        <v>48</v>
-      </c>
-      <c r="B91" s="5">
-        <v>16</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B91" s="5"/>
       <c r="C91" s="5">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D91" s="5">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B92" s="5">
-        <v>15</v>
-      </c>
-      <c r="C92" s="5">
-        <v>8</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C92" s="5"/>
       <c r="D92" s="5">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B93" s="5">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C93" s="5">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D93" s="5">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B94" s="5">
-        <v>10</v>
-      </c>
-      <c r="C94" s="5">
-        <v>12</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C94" s="5"/>
       <c r="D94" s="5">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="B95" s="5">
-        <v>10</v>
-      </c>
-      <c r="C95" s="5">
-        <v>15</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C95" s="5"/>
       <c r="D95" s="5">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B96" s="5">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C96" s="5">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D96" s="5">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B97" s="5">
-        <v>5</v>
-      </c>
-      <c r="C97" s="5">
-        <v>12</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C97" s="5"/>
       <c r="D97" s="5">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B98" s="5">
-        <v>14</v>
-      </c>
-      <c r="C98" s="5">
-        <v>6</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C98" s="5"/>
       <c r="D98" s="5">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B99" s="5">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C99" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D99" s="5">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B100" s="5">
-        <v>4</v>
-      </c>
-      <c r="C100" s="5">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C100" s="5"/>
       <c r="D100" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
-        <v>58</v>
-      </c>
-      <c r="B101" s="5">
-        <v>8</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="B101" s="5"/>
       <c r="C101" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D101" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="B102" s="5">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C102" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D102" s="5">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
-        <v>60</v>
-      </c>
-      <c r="B103" s="5">
-        <v>8</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="B103" s="5"/>
       <c r="C103" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D103" s="5">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
-        <v>61</v>
-      </c>
-      <c r="B104" s="5">
-        <v>5</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="B104" s="5"/>
       <c r="C104" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D104" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="4">
-        <v>62</v>
+      <c r="A105" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="B105" s="5">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="C105" s="5">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="D105" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="4">
-        <v>63</v>
-      </c>
-      <c r="B106" s="5">
-        <v>9</v>
-      </c>
-      <c r="C106" s="5">
-        <v>2</v>
-      </c>
-      <c r="D106" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="4">
-        <v>64</v>
-      </c>
-      <c r="B107" s="5">
-        <v>7</v>
-      </c>
-      <c r="C107" s="5">
-        <v>3</v>
-      </c>
-      <c r="D107" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="4">
-        <v>65</v>
-      </c>
-      <c r="B108" s="5">
-        <v>6</v>
-      </c>
-      <c r="C108" s="5">
-        <v>3</v>
-      </c>
-      <c r="D108" s="5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="4">
-        <v>66</v>
-      </c>
-      <c r="B109" s="5">
-        <v>8</v>
-      </c>
-      <c r="C109" s="5">
-        <v>6</v>
-      </c>
-      <c r="D109" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="4">
-        <v>67</v>
-      </c>
-      <c r="B110" s="5">
-        <v>8</v>
-      </c>
-      <c r="C110" s="5">
-        <v>2</v>
-      </c>
-      <c r="D110" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="4">
-        <v>68</v>
-      </c>
-      <c r="B111" s="5">
-        <v>3</v>
-      </c>
-      <c r="C111" s="5"/>
-      <c r="D111" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="4">
-        <v>69</v>
-      </c>
-      <c r="B112" s="5">
-        <v>8</v>
-      </c>
-      <c r="C112" s="5"/>
-      <c r="D112" s="5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="4">
-        <v>70</v>
-      </c>
-      <c r="B113" s="5">
-        <v>3</v>
-      </c>
-      <c r="C113" s="5">
-        <v>1</v>
-      </c>
-      <c r="D113" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="4">
-        <v>71</v>
-      </c>
-      <c r="B114" s="5">
-        <v>1</v>
-      </c>
-      <c r="C114" s="5"/>
-      <c r="D114" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="4">
-        <v>72</v>
-      </c>
-      <c r="B115" s="5"/>
-      <c r="C115" s="5">
-        <v>1</v>
-      </c>
-      <c r="D115" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="4">
-        <v>73</v>
-      </c>
-      <c r="B116" s="5">
-        <v>2</v>
-      </c>
-      <c r="C116" s="5">
-        <v>2</v>
-      </c>
-      <c r="D116" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="4">
-        <v>74</v>
-      </c>
-      <c r="B117" s="5"/>
-      <c r="C117" s="5">
-        <v>1</v>
-      </c>
-      <c r="D117" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="4">
-        <v>78</v>
-      </c>
-      <c r="B118" s="5">
-        <v>1</v>
-      </c>
-      <c r="C118" s="5">
-        <v>1</v>
-      </c>
-      <c r="D118" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="4">
-        <v>80</v>
-      </c>
-      <c r="B119" s="5">
-        <v>1</v>
-      </c>
-      <c r="C119" s="5"/>
-      <c r="D119" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="4">
-        <v>89</v>
-      </c>
-      <c r="B120" s="5">
-        <v>1</v>
-      </c>
-      <c r="C120" s="5"/>
-      <c r="D120" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B121" s="5">
-        <v>531</v>
-      </c>
-      <c r="C121" s="5">
-        <v>495</v>
-      </c>
-      <c r="D121" s="5">
-        <v>1026</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -31802,7 +30438,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{763730C6-0F98-4FC4-9F98-EF6134D85C9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -31910,7 +30546,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N1027"/>
   <sheetFormatPr defaultColWidth="11.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
